--- a/Mutanat - kontynuacja/4.BN/statystyki wrogów.xlsx
+++ b/Mutanat - kontynuacja/4.BN/statystyki wrogów.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pawel\Documents\WFRP\PRZYGODY\scenariusze_dla_ekipy\Mutanat - kontynuacja\4.BN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE8787B-9624-4712-AC1D-EE0C12B5D41A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDDEC1E-4495-46BB-B5EB-108E973F30B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A33956EA-54C7-4C93-9D4D-A9821C87F6DA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{A33956EA-54C7-4C93-9D4D-A9821C87F6DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
+    <sheet name="Mutant kontynuacja" sheetId="2" r:id="rId2"/>
+    <sheet name="BG" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="160">
   <si>
     <t>WW</t>
   </si>
@@ -132,13 +134,1171 @@
   </si>
   <si>
     <t>Broń Biała(Podstawowa) 38, Rzemiosło(Rzeźnictwo)</t>
+  </si>
+  <si>
+    <t>Imię</t>
+  </si>
+  <si>
+    <t>Rola/Profesja</t>
+  </si>
+  <si>
+    <t>Egon</t>
+  </si>
+  <si>
+    <t>Dietrih von Mahl</t>
+  </si>
+  <si>
+    <t>Hans Knochen</t>
+  </si>
+  <si>
+    <t>Hector Wolf</t>
+  </si>
+  <si>
+    <t>Skaven</t>
+  </si>
+  <si>
+    <t>Rajfur/Złodziej</t>
+  </si>
+  <si>
+    <t>Myśliwy</t>
+  </si>
+  <si>
+    <t>Herszt/Rzeźnik</t>
+  </si>
+  <si>
+    <t>Brutal (pałka)</t>
+  </si>
+  <si>
+    <t>Brutal(kastet)</t>
+  </si>
+  <si>
+    <t>Brutal(miecz)</t>
+  </si>
+  <si>
+    <t>Skrytobójca</t>
+  </si>
+  <si>
+    <t>Łowca czarownic</t>
+  </si>
+  <si>
+    <t>PP (Pancerz)</t>
+  </si>
+  <si>
+    <t>Broń(obrażenia)</t>
+  </si>
+  <si>
+    <t>Kluczowe talenty i Umiejętności</t>
+  </si>
+  <si>
+    <t>Sztylet(+5), Kastet(+6</t>
+  </si>
+  <si>
+    <t>Łuk krótki(+3, zas. 20), strzały(nadziewający), sztylet(+5)</t>
+  </si>
+  <si>
+    <t>Cień, Cios Poniżej Pasa, Ulicznik, Chodu!</t>
+  </si>
+  <si>
+    <t>Strzelec Wyborowy, Celny strzał, Oko Łowcy</t>
+  </si>
+  <si>
+    <t>Topór (+9, Rąbiący, Niewywazony)</t>
+  </si>
+  <si>
+    <t>Strach(1), Groźny, Silny Cios, Urodzony Wojownik</t>
+  </si>
+  <si>
+    <t>Ogłuszenie, Silny Cios</t>
+  </si>
+  <si>
+    <t>Cios Poniżej Pasa 2, Wściekły Atak</t>
+  </si>
+  <si>
+    <t>2xKastet(+8)</t>
+  </si>
+  <si>
+    <t>1 (Czepiec skórzany: głowa)</t>
+  </si>
+  <si>
+    <t>2 (Napierśnik metalowy: korpus), 1 (hełm skórzany: głowa)</t>
+  </si>
+  <si>
+    <t>1 (Kaftan skórzany: korpus, ramiona)</t>
+  </si>
+  <si>
+    <t>Krótki miecz (+8)</t>
+  </si>
+  <si>
+    <t>Silny Cios, Twardziel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (korpus), 1 (ręce, nogi, korpus)               </t>
+  </si>
+  <si>
+    <t>2xPistolet (+8, 20m, Nadziewający, Pistolet, Przebijający, Przekłuwający, Przeładowanie 1</t>
+  </si>
+  <si>
+    <t>Niugięty, Widzenie w ciemności (20m)</t>
+  </si>
+  <si>
+    <t>2xPistolet (+8, 20m), proch i 12 kul, Miecz (+7), Sztylet (+5)</t>
+  </si>
+  <si>
+    <t>1(Skórzany kaftan i spodnie: korpus, ramiona, nogi)</t>
+  </si>
+  <si>
+    <t>Bitewny Refleks, Mistrz Walki, Szczur Tunelowy, Strzał Przebijający, Zejście z Linii</t>
+  </si>
+  <si>
+    <t>Kusza pistoletowa(+9, 10m), Ogon(+5), Miecz(+7)</t>
+  </si>
+  <si>
+    <t>Strażnik miejski</t>
+  </si>
+  <si>
+    <t>1 głowa, 2 tułów, 1 ramiona(skórzana kurta, kaftan kolczy, hełm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BB(Parująca, Podstawowa, Drzewcowa), Percepcja 35, Intuicja 35, Opanowanie 40, Atletyka 40, </t>
+  </si>
+  <si>
+    <t>Miecz (+7), Halabarda (+7, Parująca, Nadziewająca albo Rąbiąca, Długa), latarnia na drągu, 1k10 SS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Żyw aktualna </t>
+  </si>
+  <si>
+    <t>Osiłek 1 Mark</t>
+  </si>
+  <si>
+    <t>Osiłek 2 Olaf</t>
+  </si>
+  <si>
+    <t>Osiłek 3 Hugo</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bitewny Refleks:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> +10 do Inicjatywy, gdy określana jest kolejność</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Szczur Tunelowy:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> W tunelach, kanałach ściekowych i pod powierzchnią ziemi, kiedy wykorzystujesz Skradanie, istotom wokoło nie przysługuje pasywny
+Test Percepcji. Zauważyć cię mogą dopiero wtedy, gdy będą cię czynnie wyglądały lub szukały ukrytych przeciwników</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Strzał Przebijający:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Kiedy
+trafisz, wykonując Test Broni Zasięgowej, możesz zignorować tyle
+Punktów Pancerza wroga, ile razy wykupiłeś ten Talent</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Zejście z linii: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jeśli wykorzystujesz
+Umiejętność Unik i wygrasz Test Przeciwstawny, możesz poruszyć się na odległość do 2 m i nie liczysz się jako związany walką. Przeciwnicy nie mogą wykonać przeciwko tobie darmowych ataków.</t>
+    </r>
+  </si>
+  <si>
+    <t>GŁadkie słówka</t>
+  </si>
+  <si>
+    <r>
+      <t>Cios Poniżej Pasa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Dodaje </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+1 do Obrażeń za każdy poziom talentu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> przy udanym trafieniu z użyciem umiejętności </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Broń Biała (Bijatyka)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Chodu!:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Zwiększa Cechę </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Szybkość (Sz) o +1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> podczas ucieczki oraz daje premię </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+10 do testów Atletyki</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> w trakcie biegu/ucieczki</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Alley Cat:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> przyznają Ułatwienie (Advantage) do testów Skradania się w toczeniu miejskim</t>
+    </r>
+  </si>
+  <si>
+    <t>Thorffin</t>
+  </si>
+  <si>
+    <t>Złodziej</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broń Biała (Podstawowa) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atletyka </t>
+  </si>
+  <si>
+    <t>Charyzma</t>
+  </si>
+  <si>
+    <t>Intuicja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odporność </t>
+  </si>
+  <si>
+    <t>Opanowanie</t>
+  </si>
+  <si>
+    <t>Percepcja</t>
+  </si>
+  <si>
+    <t>Plotkowanie</t>
+  </si>
+  <si>
+    <t>Skradanie</t>
+  </si>
+  <si>
+    <t>Targowanie</t>
+  </si>
+  <si>
+    <t>Unik</t>
+  </si>
+  <si>
+    <t>Wspinaczka</t>
+  </si>
+  <si>
+    <t>Broń zasięgowa(kusze)</t>
+  </si>
+  <si>
+    <t>Broń zasięgowa(łuki)</t>
+  </si>
+  <si>
+    <t>Otwieranie zamków</t>
+  </si>
+  <si>
+    <t>Sekretne znaki (złodziei)</t>
+  </si>
+  <si>
+    <t>Wycena</t>
+  </si>
+  <si>
+    <t>Zwinne palce</t>
+  </si>
+  <si>
+    <t>PODSTAWOWE</t>
+  </si>
+  <si>
+    <t>ZAAWANSOWANE</t>
+  </si>
+  <si>
+    <t>Chodu!</t>
+  </si>
+  <si>
+    <t>Silne nogi</t>
+  </si>
+  <si>
+    <t>Wyczucie kierunku</t>
+  </si>
+  <si>
+    <t>Ogłuszenie</t>
+  </si>
+  <si>
+    <t>Ulicznik</t>
+  </si>
+  <si>
+    <t>Etykieta (Przestępców)</t>
+  </si>
+  <si>
+    <t>TALENTY</t>
+  </si>
+  <si>
+    <t>Żebrak</t>
+  </si>
+  <si>
+    <t>Lambert</t>
+  </si>
+  <si>
+    <t>Mocna głowa</t>
+  </si>
+  <si>
+    <t>Skradanie(miasto)</t>
+  </si>
+  <si>
+    <t>Charyzmatyczny</t>
+  </si>
+  <si>
+    <t>Szczęście</t>
+  </si>
+  <si>
+    <t>Geniusz arytmetyczny</t>
+  </si>
+  <si>
+    <t>Strzelec wyborowy</t>
+  </si>
+  <si>
+    <t>Niezwykle odporny</t>
+  </si>
+  <si>
+    <t>Roman</t>
+  </si>
+  <si>
+    <t>Lekki kawalerzysta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broń Biała (Kawaleryjska) </t>
+  </si>
+  <si>
+    <t>Dowodzenie</t>
+  </si>
+  <si>
+    <t>Hazard</t>
+  </si>
+  <si>
+    <t>Jeździectwo</t>
+  </si>
+  <si>
+    <t>Sztuka przetrwania</t>
+  </si>
+  <si>
+    <t>Powożenie</t>
+  </si>
+  <si>
+    <t>Zastraszanie</t>
+  </si>
+  <si>
+    <t>Opieka nad zwierzętami</t>
+  </si>
+  <si>
+    <t>Jeździectwo(konie)</t>
+  </si>
+  <si>
+    <t>Leczenie</t>
+  </si>
+  <si>
+    <t>Język (Bitewny)</t>
+  </si>
+  <si>
+    <t>Czujny</t>
+  </si>
+  <si>
+    <t>Urodzony wojownik</t>
+  </si>
+  <si>
+    <t>Atrakcyjny</t>
+  </si>
+  <si>
+    <t>Błyskotliwy</t>
+  </si>
+  <si>
+    <t>Pierwsza pomoc</t>
+  </si>
+  <si>
+    <t>Pałka(+8, Tępa, Ogłuszająca)</t>
+  </si>
+  <si>
+    <t>Osiłek 1 Marcus</t>
+  </si>
+  <si>
+    <r>
+      <t>Nadziewający</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> :</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Trafienie Krytyczne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> przy wyniku rzutu podzielnym przez 10 (np. 10, 20, 30 itd.) oraz przy dubletach (np. 11, 22, 33)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Oko Łowcy:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pozwala ignorować kary z tytułu osłony celu (do poziomu Trudny / −20) przy atakach dystansowych.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Strzelec Wyborowy:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Daje stałą premię </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+5 do początkowej wartości Umiejętności Strzeleckich (US)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Celny Strzał:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Dodaje </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+1 do Obrażeń</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> przy atakach bronią dystansową za każdy poziom tego talentu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mistrz Walki:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gdy określana jest przewaga liczebna w walce, ty liczysz się jak jedna osoba więcej. Talent ten działa tylko wtedy, gdy przeciwników jest faktycznie więcej od grupy, w której znajduje się postać.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Rąbiąca:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Udane trafienie niszczy pancerz lub tarcze — trwale </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>obniża Punkty Pancerza (PP) lub wartość Tarczy celu o 1 poin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Niewyważona (Unbalanced):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Podczas parowania ataku wręcz, użytkownik otrzymuje karę </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>−1 PS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> do testu obrony</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Groźny:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Daje premię </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+10 (lub +1 PS)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> do wszystkich testów </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Zastraszania</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Silny Cios:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Dodaje </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+1 do Obrażeń za każdy poziom talentu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> przy wszystkich atakach w walce wręcz (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Broń Biała</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Strach (1) : Każda postać przy kontakcie musi zdać </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Opanowania (SW)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Porażka nakłada </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">karę </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>−1 PS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> do wszystkich testów** wymierzonych w Hansa i blokuje możliwość podjścia do niego w walce.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tępa (Pummel):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pancerz (PP) obrońcy jest podwajany, nie obowiązuje zasada zadawania minimum 1 Rany po udanym trafieniu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ogłuszenie:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pozwala wykonywać ataki celowane w Głowę bez standardowej kary oraz umożliwia nałożenie Stanu </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Oszołomienie</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> przy udanym trafieniu bronią tępą</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Wściekły Atak:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Po udanym trafieniu w walce wręcz pozwala wydać 1 punkt Przewagi, aby natychmiast wykonać </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dodatkowy atak wręcz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> w tej samej rundzie.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Twardziel:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Dodaje wartość </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bonusu z Wytrzymałości (BWt)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> do maksymalnej puli Żywotności postaci</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mechanika Trafień Krytycznych:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Broń ta zadaje </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Trafienie Krytyczne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> przy dowolnym wyniku rzutu podzielnym przez 10 (np. 10, 20, 30 itd.) oraz przy dubletach (np. 11, 22, 33), pod warunkiem, że rzut był udany (wynik równy lub niższy od poziomu umiejętności).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nadziewający</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:  Broń  zadaje</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Trafienie Krytyczne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> przy dowolnym wyniku rzutu podzielnym przez 10 (np. 10, 20, 30 itd.) oraz przy dubletach (np. 11, 22, 33), pod warunkiem, że rzut był udany.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,6 +1336,189 @@
       <name val="Google Sans Text"/>
       <charset val="238"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -185,7 +1528,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -193,13 +1536,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -211,11 +1594,105 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -232,10 +1709,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -893,4 +2366,1948 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CD5222A-59BB-453D-908B-8D4D1F989C4A}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="24.95" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="6" width="18.5703125" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" customWidth="1"/>
+    <col min="12" max="12" width="28.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="189" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A2" s="36"/>
+    </row>
+    <row r="3" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
+      <c r="A3" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="35" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A5" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="34">
+        <v>38</v>
+      </c>
+      <c r="C5" s="34">
+        <v>26</v>
+      </c>
+      <c r="D5" s="34">
+        <v>52</v>
+      </c>
+      <c r="E5" s="34">
+        <v>44</v>
+      </c>
+      <c r="F5" s="34">
+        <v>39</v>
+      </c>
+      <c r="G5" s="34">
+        <v>46</v>
+      </c>
+      <c r="H5" s="34">
+        <v>42</v>
+      </c>
+      <c r="I5" s="34">
+        <v>47</v>
+      </c>
+      <c r="L5" s="34">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="35" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A6" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="34">
+        <v>30</v>
+      </c>
+      <c r="C6" s="34">
+        <v>48</v>
+      </c>
+      <c r="D6" s="34">
+        <v>30</v>
+      </c>
+      <c r="E6" s="34">
+        <v>28</v>
+      </c>
+      <c r="F6" s="34">
+        <v>28</v>
+      </c>
+      <c r="G6" s="34">
+        <v>30</v>
+      </c>
+      <c r="H6" s="34">
+        <v>48</v>
+      </c>
+      <c r="I6" s="34">
+        <v>51</v>
+      </c>
+      <c r="L6" s="34">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="35" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A7" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="34">
+        <v>32</v>
+      </c>
+      <c r="C7" s="34">
+        <v>29</v>
+      </c>
+      <c r="D7" s="34">
+        <v>45</v>
+      </c>
+      <c r="E7" s="34">
+        <v>38</v>
+      </c>
+      <c r="F7" s="34">
+        <v>40</v>
+      </c>
+      <c r="G7" s="34">
+        <v>37</v>
+      </c>
+      <c r="H7" s="34">
+        <v>32</v>
+      </c>
+      <c r="I7" s="34">
+        <v>32</v>
+      </c>
+      <c r="L7" s="34">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="35" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A8" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="34">
+        <v>34</v>
+      </c>
+      <c r="C8" s="34">
+        <v>38</v>
+      </c>
+      <c r="D8" s="34">
+        <v>48</v>
+      </c>
+      <c r="E8" s="34">
+        <v>40</v>
+      </c>
+      <c r="F8" s="34">
+        <v>38</v>
+      </c>
+      <c r="G8" s="34">
+        <v>40</v>
+      </c>
+      <c r="H8" s="34">
+        <v>45</v>
+      </c>
+      <c r="I8" s="34">
+        <v>43</v>
+      </c>
+      <c r="L8" s="34">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="35" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A9" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="34">
+        <v>42</v>
+      </c>
+      <c r="C9" s="34">
+        <v>45</v>
+      </c>
+      <c r="D9" s="34">
+        <v>38</v>
+      </c>
+      <c r="E9" s="34">
+        <v>34</v>
+      </c>
+      <c r="F9" s="34">
+        <v>35</v>
+      </c>
+      <c r="G9" s="34">
+        <v>36</v>
+      </c>
+      <c r="H9" s="34">
+        <v>39</v>
+      </c>
+      <c r="I9" s="34">
+        <v>45</v>
+      </c>
+      <c r="L9" s="34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8">
+        <v>45</v>
+      </c>
+      <c r="C10" s="8">
+        <v>32</v>
+      </c>
+      <c r="D10" s="8">
+        <v>28</v>
+      </c>
+      <c r="E10" s="8">
+        <v>35</v>
+      </c>
+      <c r="F10" s="8">
+        <v>36</v>
+      </c>
+      <c r="G10" s="8">
+        <v>34</v>
+      </c>
+      <c r="H10" s="8">
+        <v>41</v>
+      </c>
+      <c r="I10" s="8">
+        <v>55</v>
+      </c>
+      <c r="L10" s="22">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8">
+        <v>40</v>
+      </c>
+      <c r="C11" s="8">
+        <v>38</v>
+      </c>
+      <c r="D11" s="8">
+        <v>32</v>
+      </c>
+      <c r="E11" s="8">
+        <v>30</v>
+      </c>
+      <c r="F11" s="8">
+        <v>30</v>
+      </c>
+      <c r="G11" s="8">
+        <v>32</v>
+      </c>
+      <c r="H11" s="8">
+        <v>24</v>
+      </c>
+      <c r="I11" s="8">
+        <v>31</v>
+      </c>
+      <c r="L11" s="22">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8">
+        <v>32</v>
+      </c>
+      <c r="C12" s="8">
+        <v>35</v>
+      </c>
+      <c r="D12" s="8">
+        <v>28</v>
+      </c>
+      <c r="E12" s="8">
+        <v>28</v>
+      </c>
+      <c r="F12" s="8">
+        <v>26</v>
+      </c>
+      <c r="G12" s="8">
+        <v>30</v>
+      </c>
+      <c r="H12" s="8">
+        <v>53</v>
+      </c>
+      <c r="I12" s="8">
+        <v>37</v>
+      </c>
+      <c r="L12" s="22">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="8">
+        <v>30</v>
+      </c>
+      <c r="C13" s="8">
+        <v>36</v>
+      </c>
+      <c r="D13" s="8">
+        <v>42</v>
+      </c>
+      <c r="E13" s="8">
+        <v>32</v>
+      </c>
+      <c r="F13" s="8">
+        <v>30</v>
+      </c>
+      <c r="G13" s="8">
+        <v>34</v>
+      </c>
+      <c r="H13" s="8">
+        <v>48</v>
+      </c>
+      <c r="I13" s="8">
+        <v>32</v>
+      </c>
+      <c r="L13" s="22">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8">
+        <v>41</v>
+      </c>
+      <c r="C14" s="8">
+        <v>30</v>
+      </c>
+      <c r="D14" s="8">
+        <v>38</v>
+      </c>
+      <c r="E14" s="8">
+        <v>28</v>
+      </c>
+      <c r="F14" s="8">
+        <v>26</v>
+      </c>
+      <c r="G14" s="8">
+        <v>28</v>
+      </c>
+      <c r="H14" s="8">
+        <v>46</v>
+      </c>
+      <c r="I14" s="8">
+        <v>24</v>
+      </c>
+      <c r="L14" s="22">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="8">
+        <v>12</v>
+      </c>
+      <c r="C15" s="8">
+        <v>14</v>
+      </c>
+      <c r="D15" s="8">
+        <v>17</v>
+      </c>
+      <c r="E15" s="8">
+        <v>13</v>
+      </c>
+      <c r="F15" s="8">
+        <v>13</v>
+      </c>
+      <c r="G15" s="8">
+        <v>17</v>
+      </c>
+      <c r="H15" s="8">
+        <v>14</v>
+      </c>
+      <c r="I15" s="8">
+        <v>14</v>
+      </c>
+      <c r="L15" s="22">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="23" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A16" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="14">
+        <v>12</v>
+      </c>
+      <c r="C16" s="14">
+        <v>14</v>
+      </c>
+      <c r="D16" s="14">
+        <v>17</v>
+      </c>
+      <c r="E16" s="14">
+        <v>13</v>
+      </c>
+      <c r="F16" s="14">
+        <v>13</v>
+      </c>
+      <c r="G16" s="14">
+        <v>17</v>
+      </c>
+      <c r="H16" s="14">
+        <v>14</v>
+      </c>
+      <c r="I16" s="14">
+        <v>14</v>
+      </c>
+      <c r="L16" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="8">
+        <v>4</v>
+      </c>
+      <c r="C17" s="8">
+        <v>3</v>
+      </c>
+      <c r="D17" s="8">
+        <v>4</v>
+      </c>
+      <c r="E17" s="8">
+        <v>4</v>
+      </c>
+      <c r="F17" s="8">
+        <v>4</v>
+      </c>
+      <c r="G17" s="8">
+        <v>4</v>
+      </c>
+      <c r="H17" s="8">
+        <v>4</v>
+      </c>
+      <c r="I17" s="8">
+        <v>6</v>
+      </c>
+      <c r="L17" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="78" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="8">
+        <v>0</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="62.25" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="77.25" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="87.75" customHeight="1">
+      <c r="B21" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="96.75" customHeight="1">
+      <c r="B22" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="117" customHeight="1">
+      <c r="B23" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="75.75" customHeight="1">
+      <c r="B24" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="I24" s="21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="110.25" customHeight="1">
+      <c r="D25" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="I25" s="21" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB4DDE17-6645-47A6-9A5F-3DCF0FF1BE32}">
+  <dimension ref="A3:F215"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="6.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:6" ht="24.95" customHeight="1" thickBot="1">
+      <c r="B3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="24.95" customHeight="1">
+      <c r="B4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="8"/>
+    </row>
+    <row r="5" spans="2:6" ht="24.95" customHeight="1">
+      <c r="B5" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="16">
+        <v>28</v>
+      </c>
+      <c r="D5" s="16">
+        <v>32</v>
+      </c>
+      <c r="E5" s="16">
+        <v>45</v>
+      </c>
+      <c r="F5" s="16"/>
+    </row>
+    <row r="6" spans="2:6" ht="24.95" customHeight="1">
+      <c r="B6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16">
+        <v>30</v>
+      </c>
+      <c r="D6" s="16">
+        <v>38</v>
+      </c>
+      <c r="E6" s="16">
+        <v>30</v>
+      </c>
+      <c r="F6" s="16"/>
+    </row>
+    <row r="7" spans="2:6" ht="24.95" customHeight="1">
+      <c r="B7" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="16">
+        <v>30</v>
+      </c>
+      <c r="D7" s="16">
+        <v>27</v>
+      </c>
+      <c r="E7" s="16">
+        <v>35</v>
+      </c>
+      <c r="F7" s="16"/>
+    </row>
+    <row r="8" spans="2:6" ht="24.95" customHeight="1">
+      <c r="B8" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="16">
+        <v>30</v>
+      </c>
+      <c r="D8" s="16">
+        <v>53</v>
+      </c>
+      <c r="E8" s="16">
+        <v>40</v>
+      </c>
+      <c r="F8" s="16"/>
+    </row>
+    <row r="9" spans="2:6" ht="24.95" customHeight="1">
+      <c r="B9" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="16">
+        <v>40</v>
+      </c>
+      <c r="D9" s="16">
+        <v>33</v>
+      </c>
+      <c r="E9" s="16">
+        <v>35</v>
+      </c>
+      <c r="F9" s="16"/>
+    </row>
+    <row r="10" spans="2:6" ht="24.95" customHeight="1">
+      <c r="B10" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="8">
+        <v>35</v>
+      </c>
+      <c r="D10" s="8">
+        <v>46</v>
+      </c>
+      <c r="E10" s="8">
+        <v>36</v>
+      </c>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="2:6" ht="24.95" customHeight="1">
+      <c r="B11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="8">
+        <v>34</v>
+      </c>
+      <c r="D11" s="8">
+        <v>35</v>
+      </c>
+      <c r="E11" s="8">
+        <v>32</v>
+      </c>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="2:6" ht="24.95" customHeight="1">
+      <c r="B12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="8">
+        <v>32</v>
+      </c>
+      <c r="D12" s="8">
+        <v>37</v>
+      </c>
+      <c r="E12" s="8">
+        <v>37</v>
+      </c>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="2:6" ht="24.95" customHeight="1">
+      <c r="B13" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="8">
+        <v>30</v>
+      </c>
+      <c r="D13" s="8">
+        <v>37</v>
+      </c>
+      <c r="E13" s="8">
+        <v>31</v>
+      </c>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="2:6" ht="24.95" customHeight="1">
+      <c r="B14" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="8">
+        <v>40</v>
+      </c>
+      <c r="D14" s="8">
+        <v>46</v>
+      </c>
+      <c r="E14" s="8">
+        <v>28</v>
+      </c>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="2:6" ht="24.95" customHeight="1">
+      <c r="B15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="8">
+        <v>12</v>
+      </c>
+      <c r="D15" s="8">
+        <v>15</v>
+      </c>
+      <c r="E15" s="8">
+        <v>14</v>
+      </c>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="2:6" s="23" customFormat="1" ht="24.95" customHeight="1">
+      <c r="B16" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="14">
+        <v>12</v>
+      </c>
+      <c r="D16" s="14">
+        <v>15</v>
+      </c>
+      <c r="E16" s="14">
+        <v>14</v>
+      </c>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" spans="1:6" ht="24.95" customHeight="1">
+      <c r="B17" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="8">
+        <v>4</v>
+      </c>
+      <c r="D17" s="8">
+        <v>4</v>
+      </c>
+      <c r="E17" s="8">
+        <v>4</v>
+      </c>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="1:6" ht="78" customHeight="1">
+      <c r="B18" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+    </row>
+    <row r="19" spans="1:6" ht="62.25" customHeight="1">
+      <c r="B19" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+    </row>
+    <row r="20" spans="1:6" ht="15" customHeight="1">
+      <c r="A20" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="30">
+        <v>40</v>
+      </c>
+      <c r="D20" s="30">
+        <v>51</v>
+      </c>
+      <c r="E20" s="30">
+        <v>36</v>
+      </c>
+      <c r="F20" s="19"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="39"/>
+      <c r="B21" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="31">
+        <v>30</v>
+      </c>
+      <c r="D21" s="31">
+        <v>38</v>
+      </c>
+      <c r="E21" s="30">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="39"/>
+      <c r="B22" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" s="31">
+        <v>28</v>
+      </c>
+      <c r="D22" s="31">
+        <v>32</v>
+      </c>
+      <c r="E22" s="30">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="39"/>
+      <c r="B23" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="30">
+        <v>45</v>
+      </c>
+      <c r="D23" s="31">
+        <v>66</v>
+      </c>
+      <c r="E23" s="30">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="39"/>
+      <c r="B24" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="30">
+        <v>40</v>
+      </c>
+      <c r="D24" s="31">
+        <v>46</v>
+      </c>
+      <c r="E24" s="30">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="39"/>
+      <c r="B25" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="30">
+        <v>32</v>
+      </c>
+      <c r="D25" s="31">
+        <v>37</v>
+      </c>
+      <c r="E25" s="30">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="39"/>
+      <c r="B26" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="30">
+        <v>50</v>
+      </c>
+      <c r="D26" s="31">
+        <v>38</v>
+      </c>
+      <c r="E26" s="30">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="39"/>
+      <c r="B27" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="30">
+        <v>35</v>
+      </c>
+      <c r="D27" s="31">
+        <v>46</v>
+      </c>
+      <c r="E27" s="30">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="39"/>
+      <c r="B28" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C28" s="30">
+        <v>30</v>
+      </c>
+      <c r="D28" s="31">
+        <v>58</v>
+      </c>
+      <c r="E28" s="30">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="39"/>
+      <c r="B29" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="30">
+        <v>35</v>
+      </c>
+      <c r="D29" s="31">
+        <v>58</v>
+      </c>
+      <c r="E29" s="30">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="39"/>
+      <c r="B30" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="30">
+        <v>35</v>
+      </c>
+      <c r="D30" s="31">
+        <v>47</v>
+      </c>
+      <c r="E30" s="30">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="39"/>
+      <c r="B31" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="30">
+        <v>50</v>
+      </c>
+      <c r="D31" s="31">
+        <v>34</v>
+      </c>
+      <c r="E31" s="30">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="39"/>
+      <c r="B32" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" s="30">
+        <v>45</v>
+      </c>
+      <c r="D32" s="31">
+        <v>49</v>
+      </c>
+      <c r="E32" s="30">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="39"/>
+      <c r="B33" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="30">
+        <v>35</v>
+      </c>
+      <c r="D33" s="31">
+        <v>46</v>
+      </c>
+      <c r="E33" s="30">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="39"/>
+      <c r="B34" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34" s="30">
+        <v>40</v>
+      </c>
+      <c r="D34" s="31">
+        <v>46</v>
+      </c>
+      <c r="E34" s="30">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="39"/>
+      <c r="B35" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" s="30">
+        <v>32</v>
+      </c>
+      <c r="D35" s="31">
+        <v>37</v>
+      </c>
+      <c r="E35" s="30">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="39"/>
+      <c r="B36" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" s="30">
+        <v>43</v>
+      </c>
+      <c r="D36" s="31">
+        <v>49</v>
+      </c>
+      <c r="E36" s="30">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="39"/>
+      <c r="B37" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="30">
+        <v>40</v>
+      </c>
+      <c r="D37" s="31">
+        <v>51</v>
+      </c>
+      <c r="E37" s="30">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="39"/>
+      <c r="B38" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38" s="30">
+        <v>40</v>
+      </c>
+      <c r="D38" s="31">
+        <v>27</v>
+      </c>
+      <c r="E38" s="30">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="39"/>
+      <c r="B39" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" s="30">
+        <v>30</v>
+      </c>
+      <c r="D39" s="31">
+        <v>27</v>
+      </c>
+      <c r="E39" s="31">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="C40" s="20"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="20"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="30">
+        <v>35</v>
+      </c>
+      <c r="D41" s="31"/>
+      <c r="E41" s="20"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="38"/>
+      <c r="B42" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42" s="30">
+        <v>35</v>
+      </c>
+      <c r="D42" s="31">
+        <v>43</v>
+      </c>
+      <c r="E42" s="31"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="38"/>
+      <c r="B43" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="C43" s="30"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="38"/>
+      <c r="B44" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" s="30"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="38"/>
+      <c r="B45" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" s="30"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="38"/>
+      <c r="B46" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" s="30"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="38"/>
+      <c r="B47" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="32">
+        <v>38</v>
+      </c>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="38"/>
+      <c r="B48" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C48" s="30">
+        <v>36</v>
+      </c>
+      <c r="D48" s="31"/>
+      <c r="E48" s="20"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="38"/>
+      <c r="B49" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="30">
+        <v>40</v>
+      </c>
+      <c r="D49" s="31">
+        <v>51</v>
+      </c>
+      <c r="E49" s="20"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="38"/>
+      <c r="B50" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="32">
+        <v>35</v>
+      </c>
+      <c r="D50" s="31"/>
+      <c r="E50" s="20"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="38"/>
+      <c r="B51" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C51" s="32">
+        <v>35</v>
+      </c>
+      <c r="D51" s="31">
+        <v>42</v>
+      </c>
+      <c r="E51" s="20"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="D52" s="28"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="B53" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D53" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="E53" s="29" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="B54" s="40"/>
+      <c r="C54" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D54" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="E54" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="B55" s="40"/>
+      <c r="C55" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D55" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="E55" s="29" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="B56" s="40"/>
+      <c r="C56" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="E56" s="29" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="B57" s="40"/>
+      <c r="C57" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="E57" s="29" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="B58" s="40"/>
+      <c r="C58" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D58" s="28"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="B59" s="40"/>
+      <c r="C59" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="D59" s="28"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="B60" s="40"/>
+      <c r="D60" s="28"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="D61" s="28"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="D62" s="28"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="D63" s="28"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="D64" s="28"/>
+    </row>
+    <row r="65" spans="4:4">
+      <c r="D65" s="28"/>
+    </row>
+    <row r="66" spans="4:4">
+      <c r="D66" s="28"/>
+    </row>
+    <row r="67" spans="4:4">
+      <c r="D67" s="28"/>
+    </row>
+    <row r="68" spans="4:4">
+      <c r="D68" s="28"/>
+    </row>
+    <row r="69" spans="4:4">
+      <c r="D69" s="28"/>
+    </row>
+    <row r="70" spans="4:4">
+      <c r="D70" s="28"/>
+    </row>
+    <row r="71" spans="4:4">
+      <c r="D71" s="28"/>
+    </row>
+    <row r="72" spans="4:4">
+      <c r="D72" s="28"/>
+    </row>
+    <row r="73" spans="4:4">
+      <c r="D73" s="28"/>
+    </row>
+    <row r="74" spans="4:4">
+      <c r="D74" s="28"/>
+    </row>
+    <row r="75" spans="4:4">
+      <c r="D75" s="28"/>
+    </row>
+    <row r="76" spans="4:4">
+      <c r="D76" s="28"/>
+    </row>
+    <row r="77" spans="4:4">
+      <c r="D77" s="28"/>
+    </row>
+    <row r="78" spans="4:4">
+      <c r="D78" s="28"/>
+    </row>
+    <row r="79" spans="4:4">
+      <c r="D79" s="28"/>
+    </row>
+    <row r="80" spans="4:4">
+      <c r="D80" s="28"/>
+    </row>
+    <row r="81" spans="4:4">
+      <c r="D81" s="28"/>
+    </row>
+    <row r="82" spans="4:4">
+      <c r="D82" s="28"/>
+    </row>
+    <row r="83" spans="4:4">
+      <c r="D83" s="28"/>
+    </row>
+    <row r="84" spans="4:4">
+      <c r="D84" s="28"/>
+    </row>
+    <row r="85" spans="4:4">
+      <c r="D85" s="28"/>
+    </row>
+    <row r="86" spans="4:4">
+      <c r="D86" s="28"/>
+    </row>
+    <row r="87" spans="4:4">
+      <c r="D87" s="28"/>
+    </row>
+    <row r="88" spans="4:4">
+      <c r="D88" s="28"/>
+    </row>
+    <row r="89" spans="4:4">
+      <c r="D89" s="28"/>
+    </row>
+    <row r="90" spans="4:4">
+      <c r="D90" s="28"/>
+    </row>
+    <row r="91" spans="4:4">
+      <c r="D91" s="28"/>
+    </row>
+    <row r="92" spans="4:4">
+      <c r="D92" s="28"/>
+    </row>
+    <row r="93" spans="4:4">
+      <c r="D93" s="28"/>
+    </row>
+    <row r="94" spans="4:4">
+      <c r="D94" s="28"/>
+    </row>
+    <row r="95" spans="4:4">
+      <c r="D95" s="28"/>
+    </row>
+    <row r="96" spans="4:4">
+      <c r="D96" s="28"/>
+    </row>
+    <row r="97" spans="4:4">
+      <c r="D97" s="28"/>
+    </row>
+    <row r="98" spans="4:4">
+      <c r="D98" s="28"/>
+    </row>
+    <row r="99" spans="4:4">
+      <c r="D99" s="28"/>
+    </row>
+    <row r="100" spans="4:4">
+      <c r="D100" s="28"/>
+    </row>
+    <row r="101" spans="4:4">
+      <c r="D101" s="28"/>
+    </row>
+    <row r="102" spans="4:4">
+      <c r="D102" s="28"/>
+    </row>
+    <row r="103" spans="4:4">
+      <c r="D103" s="28"/>
+    </row>
+    <row r="104" spans="4:4">
+      <c r="D104" s="28"/>
+    </row>
+    <row r="105" spans="4:4">
+      <c r="D105" s="28"/>
+    </row>
+    <row r="106" spans="4:4">
+      <c r="D106" s="28"/>
+    </row>
+    <row r="107" spans="4:4">
+      <c r="D107" s="28"/>
+    </row>
+    <row r="108" spans="4:4">
+      <c r="D108" s="28"/>
+    </row>
+    <row r="109" spans="4:4">
+      <c r="D109" s="28"/>
+    </row>
+    <row r="110" spans="4:4">
+      <c r="D110" s="28"/>
+    </row>
+    <row r="111" spans="4:4">
+      <c r="D111" s="28"/>
+    </row>
+    <row r="112" spans="4:4">
+      <c r="D112" s="28"/>
+    </row>
+    <row r="113" spans="4:4">
+      <c r="D113" s="28"/>
+    </row>
+    <row r="114" spans="4:4">
+      <c r="D114" s="28"/>
+    </row>
+    <row r="115" spans="4:4">
+      <c r="D115" s="28"/>
+    </row>
+    <row r="116" spans="4:4">
+      <c r="D116" s="28"/>
+    </row>
+    <row r="117" spans="4:4">
+      <c r="D117" s="28"/>
+    </row>
+    <row r="118" spans="4:4">
+      <c r="D118" s="28"/>
+    </row>
+    <row r="119" spans="4:4">
+      <c r="D119" s="28"/>
+    </row>
+    <row r="120" spans="4:4">
+      <c r="D120" s="28"/>
+    </row>
+    <row r="121" spans="4:4">
+      <c r="D121" s="28"/>
+    </row>
+    <row r="122" spans="4:4">
+      <c r="D122" s="28"/>
+    </row>
+    <row r="123" spans="4:4">
+      <c r="D123" s="28"/>
+    </row>
+    <row r="124" spans="4:4">
+      <c r="D124" s="28"/>
+    </row>
+    <row r="125" spans="4:4">
+      <c r="D125" s="28"/>
+    </row>
+    <row r="126" spans="4:4">
+      <c r="D126" s="28"/>
+    </row>
+    <row r="127" spans="4:4">
+      <c r="D127" s="28"/>
+    </row>
+    <row r="128" spans="4:4">
+      <c r="D128" s="28"/>
+    </row>
+    <row r="129" spans="4:4">
+      <c r="D129" s="28"/>
+    </row>
+    <row r="130" spans="4:4">
+      <c r="D130" s="28"/>
+    </row>
+    <row r="131" spans="4:4">
+      <c r="D131" s="28"/>
+    </row>
+    <row r="132" spans="4:4">
+      <c r="D132" s="28"/>
+    </row>
+    <row r="133" spans="4:4">
+      <c r="D133" s="28"/>
+    </row>
+    <row r="134" spans="4:4">
+      <c r="D134" s="28"/>
+    </row>
+    <row r="135" spans="4:4">
+      <c r="D135" s="28"/>
+    </row>
+    <row r="136" spans="4:4">
+      <c r="D136" s="28"/>
+    </row>
+    <row r="137" spans="4:4">
+      <c r="D137" s="28"/>
+    </row>
+    <row r="138" spans="4:4">
+      <c r="D138" s="28"/>
+    </row>
+    <row r="139" spans="4:4">
+      <c r="D139" s="28"/>
+    </row>
+    <row r="140" spans="4:4">
+      <c r="D140" s="28"/>
+    </row>
+    <row r="141" spans="4:4">
+      <c r="D141" s="28"/>
+    </row>
+    <row r="142" spans="4:4">
+      <c r="D142" s="28"/>
+    </row>
+    <row r="143" spans="4:4">
+      <c r="D143" s="28"/>
+    </row>
+    <row r="144" spans="4:4">
+      <c r="D144" s="28"/>
+    </row>
+    <row r="145" spans="4:4">
+      <c r="D145" s="28"/>
+    </row>
+    <row r="146" spans="4:4">
+      <c r="D146" s="28"/>
+    </row>
+    <row r="147" spans="4:4">
+      <c r="D147" s="28"/>
+    </row>
+    <row r="148" spans="4:4">
+      <c r="D148" s="28"/>
+    </row>
+    <row r="149" spans="4:4">
+      <c r="D149" s="28"/>
+    </row>
+    <row r="150" spans="4:4">
+      <c r="D150" s="28"/>
+    </row>
+    <row r="151" spans="4:4">
+      <c r="D151" s="28"/>
+    </row>
+    <row r="152" spans="4:4">
+      <c r="D152" s="28"/>
+    </row>
+    <row r="153" spans="4:4">
+      <c r="D153" s="28"/>
+    </row>
+    <row r="154" spans="4:4">
+      <c r="D154" s="28"/>
+    </row>
+    <row r="155" spans="4:4">
+      <c r="D155" s="28"/>
+    </row>
+    <row r="156" spans="4:4">
+      <c r="D156" s="28"/>
+    </row>
+    <row r="157" spans="4:4">
+      <c r="D157" s="28"/>
+    </row>
+    <row r="158" spans="4:4">
+      <c r="D158" s="28"/>
+    </row>
+    <row r="159" spans="4:4">
+      <c r="D159" s="28"/>
+    </row>
+    <row r="160" spans="4:4">
+      <c r="D160" s="28"/>
+    </row>
+    <row r="161" spans="4:4">
+      <c r="D161" s="28"/>
+    </row>
+    <row r="162" spans="4:4">
+      <c r="D162" s="28"/>
+    </row>
+    <row r="163" spans="4:4">
+      <c r="D163" s="28"/>
+    </row>
+    <row r="164" spans="4:4">
+      <c r="D164" s="28"/>
+    </row>
+    <row r="165" spans="4:4">
+      <c r="D165" s="28"/>
+    </row>
+    <row r="166" spans="4:4">
+      <c r="D166" s="28"/>
+    </row>
+    <row r="167" spans="4:4">
+      <c r="D167" s="28"/>
+    </row>
+    <row r="168" spans="4:4">
+      <c r="D168" s="28"/>
+    </row>
+    <row r="169" spans="4:4">
+      <c r="D169" s="28"/>
+    </row>
+    <row r="170" spans="4:4">
+      <c r="D170" s="28"/>
+    </row>
+    <row r="171" spans="4:4">
+      <c r="D171" s="28"/>
+    </row>
+    <row r="172" spans="4:4">
+      <c r="D172" s="28"/>
+    </row>
+    <row r="173" spans="4:4">
+      <c r="D173" s="28"/>
+    </row>
+    <row r="174" spans="4:4">
+      <c r="D174" s="28"/>
+    </row>
+    <row r="175" spans="4:4">
+      <c r="D175" s="28"/>
+    </row>
+    <row r="176" spans="4:4">
+      <c r="D176" s="28"/>
+    </row>
+    <row r="177" spans="4:4">
+      <c r="D177" s="28"/>
+    </row>
+    <row r="178" spans="4:4">
+      <c r="D178" s="28"/>
+    </row>
+    <row r="179" spans="4:4">
+      <c r="D179" s="28"/>
+    </row>
+    <row r="180" spans="4:4">
+      <c r="D180" s="28"/>
+    </row>
+    <row r="181" spans="4:4">
+      <c r="D181" s="28"/>
+    </row>
+    <row r="182" spans="4:4">
+      <c r="D182" s="28"/>
+    </row>
+    <row r="183" spans="4:4">
+      <c r="D183" s="28"/>
+    </row>
+    <row r="184" spans="4:4">
+      <c r="D184" s="28"/>
+    </row>
+    <row r="185" spans="4:4">
+      <c r="D185" s="28"/>
+    </row>
+    <row r="186" spans="4:4">
+      <c r="D186" s="28"/>
+    </row>
+    <row r="187" spans="4:4">
+      <c r="D187" s="28"/>
+    </row>
+    <row r="188" spans="4:4">
+      <c r="D188" s="28"/>
+    </row>
+    <row r="189" spans="4:4">
+      <c r="D189" s="28"/>
+    </row>
+    <row r="190" spans="4:4">
+      <c r="D190" s="28"/>
+    </row>
+    <row r="191" spans="4:4">
+      <c r="D191" s="28"/>
+    </row>
+    <row r="192" spans="4:4">
+      <c r="D192" s="28"/>
+    </row>
+    <row r="193" spans="4:4">
+      <c r="D193" s="28"/>
+    </row>
+    <row r="194" spans="4:4">
+      <c r="D194" s="28"/>
+    </row>
+    <row r="195" spans="4:4">
+      <c r="D195" s="28"/>
+    </row>
+    <row r="196" spans="4:4">
+      <c r="D196" s="28"/>
+    </row>
+    <row r="197" spans="4:4">
+      <c r="D197" s="28"/>
+    </row>
+    <row r="198" spans="4:4">
+      <c r="D198" s="28"/>
+    </row>
+    <row r="199" spans="4:4">
+      <c r="D199" s="28"/>
+    </row>
+    <row r="200" spans="4:4">
+      <c r="D200" s="28"/>
+    </row>
+    <row r="201" spans="4:4">
+      <c r="D201" s="28"/>
+    </row>
+    <row r="202" spans="4:4">
+      <c r="D202" s="28"/>
+    </row>
+    <row r="203" spans="4:4">
+      <c r="D203" s="28"/>
+    </row>
+    <row r="204" spans="4:4">
+      <c r="D204" s="28"/>
+    </row>
+    <row r="205" spans="4:4">
+      <c r="D205" s="28"/>
+    </row>
+    <row r="206" spans="4:4">
+      <c r="D206" s="28"/>
+    </row>
+    <row r="207" spans="4:4">
+      <c r="D207" s="28"/>
+    </row>
+    <row r="208" spans="4:4">
+      <c r="D208" s="28"/>
+    </row>
+    <row r="209" spans="4:4">
+      <c r="D209" s="28"/>
+    </row>
+    <row r="210" spans="4:4">
+      <c r="D210" s="28"/>
+    </row>
+    <row r="211" spans="4:4">
+      <c r="D211" s="28"/>
+    </row>
+    <row r="212" spans="4:4">
+      <c r="D212" s="28"/>
+    </row>
+    <row r="213" spans="4:4">
+      <c r="D213" s="28"/>
+    </row>
+    <row r="214" spans="4:4">
+      <c r="D214" s="28"/>
+    </row>
+    <row r="215" spans="4:4">
+      <c r="D215" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A41:A51"/>
+    <mergeCell ref="A20:A39"/>
+    <mergeCell ref="B53:B60"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Mutanat - kontynuacja/4.BN/statystyki wrogów.xlsx
+++ b/Mutanat - kontynuacja/4.BN/statystyki wrogów.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pawel\Documents\WFRP\PRZYGODY\scenariusze_dla_ekipy\Mutanat - kontynuacja\4.BN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDDEC1E-4495-46BB-B5EB-108E973F30B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79A6260-190A-4D86-BD89-5E8C11FCFA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{A33956EA-54C7-4C93-9D4D-A9821C87F6DA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{A33956EA-54C7-4C93-9D4D-A9821C87F6DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="BG" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="164">
   <si>
     <t>WW</t>
   </si>
@@ -142,15 +143,6 @@
     <t>Rola/Profesja</t>
   </si>
   <si>
-    <t>Egon</t>
-  </si>
-  <si>
-    <t>Dietrih von Mahl</t>
-  </si>
-  <si>
-    <t>Hans Knochen</t>
-  </si>
-  <si>
     <t>Hector Wolf</t>
   </si>
   <si>
@@ -169,9 +161,6 @@
     <t>Brutal (pałka)</t>
   </si>
   <si>
-    <t>Brutal(kastet)</t>
-  </si>
-  <si>
     <t>Brutal(miecz)</t>
   </si>
   <si>
@@ -214,18 +203,9 @@
     <t>Cios Poniżej Pasa 2, Wściekły Atak</t>
   </si>
   <si>
-    <t>2xKastet(+8)</t>
-  </si>
-  <si>
     <t>1 (Czepiec skórzany: głowa)</t>
   </si>
   <si>
-    <t>2 (Napierśnik metalowy: korpus), 1 (hełm skórzany: głowa)</t>
-  </si>
-  <si>
-    <t>1 (Kaftan skórzany: korpus, ramiona)</t>
-  </si>
-  <si>
     <t>Krótki miecz (+8)</t>
   </si>
   <si>
@@ -269,9 +249,6 @@
   </si>
   <si>
     <t>Osiłek 1 Mark</t>
-  </si>
-  <si>
-    <t>Osiłek 2 Olaf</t>
   </si>
   <si>
     <t>Osiłek 3 Hugo</t>
@@ -1292,6 +1269,42 @@
       </rPr>
       <t xml:space="preserve"> przy dowolnym wyniku rzutu podzielnym przez 10 (np. 10, 20, 30 itd.) oraz przy dubletach (np. 11, 22, 33), pod warunkiem, że rzut był udany.</t>
     </r>
+  </si>
+  <si>
+    <t>Bandyta_1</t>
+  </si>
+  <si>
+    <t>Skórzana kurta 4PP korpus</t>
+  </si>
+  <si>
+    <t>OLAF</t>
+  </si>
+  <si>
+    <t>HANS Knochen</t>
+  </si>
+  <si>
+    <t>DIETRICH von Mahl</t>
+  </si>
+  <si>
+    <t>EGON</t>
+  </si>
+  <si>
+    <t>1 (Kaftan skórzany: korpus 4PP, ramiona 4PP)</t>
+  </si>
+  <si>
+    <t>2 (Napierśnik metalowy ), 1 (hełm skórzany) głowa 5PP, korpus 6PP</t>
+  </si>
+  <si>
+    <t>1 (Czepiec skórzany: ) głowa 4PP</t>
+  </si>
+  <si>
+    <t>kastet (+8)</t>
+  </si>
+  <si>
+    <t>Bandyta_2</t>
+  </si>
+  <si>
+    <t>pałka(+7, ogłuszająca)</t>
   </si>
 </sst>
 </file>
@@ -1580,7 +1593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1693,6 +1706,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2370,93 +2386,110 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CD5222A-59BB-453D-908B-8D4D1F989C4A}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.5703125" customWidth="1"/>
     <col min="4" max="4" width="21.5703125" customWidth="1"/>
-    <col min="5" max="6" width="18.5703125" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" customWidth="1"/>
-    <col min="9" max="9" width="25.42578125" customWidth="1"/>
-    <col min="12" max="12" width="28.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="23.140625" customWidth="1"/>
+    <col min="9" max="10" width="20.7109375" customWidth="1"/>
+    <col min="11" max="11" width="28.140625" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" customWidth="1"/>
+    <col min="13" max="13" width="25.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="189" customHeight="1">
+    <row r="1" spans="1:13" ht="189" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="24.95" customHeight="1">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="24.95" customHeight="1">
       <c r="A2" s="36"/>
     </row>
-    <row r="3" spans="1:12" ht="24.95" customHeight="1" thickBot="1">
+    <row r="3" spans="1:13" ht="24.95" customHeight="1" thickBot="1">
       <c r="A3" s="37" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="L3" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="24.95" customHeight="1">
+    </row>
+    <row r="4" spans="1:13" ht="24.95" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="G4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="35" customFormat="1" ht="24.95" customHeight="1">
+    </row>
+    <row r="5" spans="1:13" s="35" customFormat="1" ht="24.95" customHeight="1">
       <c r="A5" s="33" t="s">
         <v>0</v>
       </c>
@@ -2479,16 +2512,23 @@
         <v>46</v>
       </c>
       <c r="H5" s="34">
+        <v>35</v>
+      </c>
+      <c r="I5" s="34">
+        <v>35</v>
+      </c>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34">
+        <v>40</v>
+      </c>
+      <c r="L5" s="34">
         <v>42</v>
       </c>
-      <c r="I5" s="34">
+      <c r="M5" s="34">
         <v>47</v>
       </c>
-      <c r="L5" s="34">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" s="35" customFormat="1" ht="24.95" customHeight="1">
+    </row>
+    <row r="6" spans="1:13" s="35" customFormat="1" ht="24.95" customHeight="1">
       <c r="A6" s="33" t="s">
         <v>1</v>
       </c>
@@ -2511,16 +2551,23 @@
         <v>30</v>
       </c>
       <c r="H6" s="34">
+        <v>32</v>
+      </c>
+      <c r="I6" s="34">
+        <v>32</v>
+      </c>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34">
+        <v>32</v>
+      </c>
+      <c r="L6" s="34">
         <v>48</v>
       </c>
-      <c r="I6" s="34">
+      <c r="M6" s="34">
         <v>51</v>
       </c>
-      <c r="L6" s="34">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="35" customFormat="1" ht="24.95" customHeight="1">
+    </row>
+    <row r="7" spans="1:13" s="35" customFormat="1" ht="24.95" customHeight="1">
       <c r="A7" s="33" t="s">
         <v>3</v>
       </c>
@@ -2543,16 +2590,23 @@
         <v>37</v>
       </c>
       <c r="H7" s="34">
+        <v>38</v>
+      </c>
+      <c r="I7" s="34">
+        <v>38</v>
+      </c>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34">
+        <v>38</v>
+      </c>
+      <c r="L7" s="34">
         <v>32</v>
       </c>
-      <c r="I7" s="34">
+      <c r="M7" s="34">
         <v>32</v>
       </c>
-      <c r="L7" s="34">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="35" customFormat="1" ht="24.95" customHeight="1">
+    </row>
+    <row r="8" spans="1:13" s="35" customFormat="1" ht="24.95" customHeight="1">
       <c r="A8" s="33" t="s">
         <v>4</v>
       </c>
@@ -2575,16 +2629,23 @@
         <v>40</v>
       </c>
       <c r="H8" s="34">
+        <v>35</v>
+      </c>
+      <c r="I8" s="34">
+        <v>35</v>
+      </c>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34">
+        <v>42</v>
+      </c>
+      <c r="L8" s="34">
         <v>45</v>
       </c>
-      <c r="I8" s="34">
+      <c r="M8" s="34">
         <v>43</v>
       </c>
-      <c r="L8" s="34">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="35" customFormat="1" ht="24.95" customHeight="1">
+    </row>
+    <row r="9" spans="1:13" s="35" customFormat="1" ht="24.95" customHeight="1">
       <c r="A9" s="33" t="s">
         <v>5</v>
       </c>
@@ -2607,16 +2668,23 @@
         <v>36</v>
       </c>
       <c r="H9" s="34">
+        <v>33</v>
+      </c>
+      <c r="I9" s="34">
+        <v>33</v>
+      </c>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34">
+        <v>33</v>
+      </c>
+      <c r="L9" s="34">
         <v>39</v>
       </c>
-      <c r="I9" s="34">
+      <c r="M9" s="34">
         <v>45</v>
       </c>
-      <c r="L9" s="34">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="24.95" customHeight="1">
+    </row>
+    <row r="10" spans="1:13" ht="24.95" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>6</v>
       </c>
@@ -2638,17 +2706,24 @@
       <c r="G10" s="8">
         <v>34</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="22">
+        <v>35</v>
+      </c>
+      <c r="I10" s="22">
+        <v>35</v>
+      </c>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22">
+        <v>35</v>
+      </c>
+      <c r="L10" s="8">
         <v>41</v>
       </c>
-      <c r="I10" s="8">
+      <c r="M10" s="8">
         <v>55</v>
       </c>
-      <c r="L10" s="22">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="24.95" customHeight="1">
+    </row>
+    <row r="11" spans="1:13" ht="24.95" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>7</v>
       </c>
@@ -2670,17 +2745,24 @@
       <c r="G11" s="8">
         <v>32</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="22">
+        <v>31</v>
+      </c>
+      <c r="I11" s="22">
+        <v>31</v>
+      </c>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22">
+        <v>31</v>
+      </c>
+      <c r="L11" s="8">
         <v>24</v>
       </c>
-      <c r="I11" s="8">
+      <c r="M11" s="8">
         <v>31</v>
       </c>
-      <c r="L11" s="22">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="24.95" customHeight="1">
+    </row>
+    <row r="12" spans="1:13" ht="24.95" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>8</v>
       </c>
@@ -2702,17 +2784,24 @@
       <c r="G12" s="8">
         <v>30</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="22">
+        <v>35</v>
+      </c>
+      <c r="I12" s="22">
+        <v>35</v>
+      </c>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22">
+        <v>35</v>
+      </c>
+      <c r="L12" s="8">
         <v>53</v>
       </c>
-      <c r="I12" s="8">
+      <c r="M12" s="8">
         <v>37</v>
       </c>
-      <c r="L12" s="22">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="24.95" customHeight="1">
+    </row>
+    <row r="13" spans="1:13" ht="24.95" customHeight="1">
       <c r="A13" s="9" t="s">
         <v>9</v>
       </c>
@@ -2734,17 +2823,24 @@
       <c r="G13" s="8">
         <v>34</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="22">
+        <v>32</v>
+      </c>
+      <c r="I13" s="22">
+        <v>32</v>
+      </c>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22">
+        <v>32</v>
+      </c>
+      <c r="L13" s="8">
         <v>48</v>
       </c>
-      <c r="I13" s="8">
+      <c r="M13" s="8">
         <v>32</v>
       </c>
-      <c r="L13" s="22">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="24.95" customHeight="1">
+    </row>
+    <row r="14" spans="1:13" ht="24.95" customHeight="1">
       <c r="A14" s="9" t="s">
         <v>10</v>
       </c>
@@ -2766,17 +2862,24 @@
       <c r="G14" s="8">
         <v>28</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="22">
+        <v>34</v>
+      </c>
+      <c r="I14" s="22">
+        <v>34</v>
+      </c>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22">
+        <v>34</v>
+      </c>
+      <c r="L14" s="8">
         <v>46</v>
       </c>
-      <c r="I14" s="8">
+      <c r="M14" s="8">
         <v>24</v>
       </c>
-      <c r="L14" s="22">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="24.95" customHeight="1">
+    </row>
+    <row r="15" spans="1:13" ht="24.95" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>11</v>
       </c>
@@ -2798,25 +2901,32 @@
       <c r="G15" s="8">
         <v>17</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="22">
+        <v>12</v>
+      </c>
+      <c r="I15" s="22">
+        <v>12</v>
+      </c>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22">
         <v>14</v>
       </c>
-      <c r="I15" s="8">
+      <c r="L15" s="8">
         <v>14</v>
       </c>
-      <c r="L15" s="22">
+      <c r="M15" s="8">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="23" customFormat="1" ht="24.95" customHeight="1">
+    <row r="16" spans="1:13" s="23" customFormat="1" ht="24.95" customHeight="1">
       <c r="A16" s="13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B16" s="14">
         <v>12</v>
       </c>
       <c r="C16" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D16" s="14">
         <v>17</v>
@@ -2831,16 +2941,23 @@
         <v>17</v>
       </c>
       <c r="H16" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I16" s="14">
+        <v>12</v>
+      </c>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14">
         <v>14</v>
       </c>
       <c r="L16" s="14">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="24.95" customHeight="1">
+      <c r="M16" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="24.95" customHeight="1">
       <c r="A17" s="9" t="s">
         <v>2</v>
       </c>
@@ -2862,195 +2979,214 @@
       <c r="G17" s="8">
         <v>4</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="22">
         <v>4</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="22">
+        <v>4</v>
+      </c>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22">
+        <v>4</v>
+      </c>
+      <c r="L17" s="8">
+        <v>4</v>
+      </c>
+      <c r="M17" s="8">
         <v>6</v>
       </c>
-      <c r="L17" s="22">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="78" customHeight="1">
+    </row>
+    <row r="18" spans="1:13" ht="78" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B18" s="8">
         <v>0</v>
       </c>
       <c r="C18" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="M18" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="19" t="s">
+    </row>
+    <row r="19" spans="1:13" ht="62.25" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="H19" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="I19" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="J19" s="20"/>
+      <c r="K19" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="L19" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="M19" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="77.25" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="L20" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="I18" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="L18" s="19" t="s">
+      <c r="M20" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="87.75" customHeight="1">
+      <c r="B21" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="7"/>
+      <c r="M21" s="21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="96.75" customHeight="1">
+      <c r="B22" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="M22" s="21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="117" customHeight="1">
+      <c r="B23" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="M23" s="21" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="62.25" customHeight="1">
-      <c r="A19" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="H19" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="19" t="s">
+    <row r="24" spans="1:13" ht="75.75" customHeight="1">
+      <c r="B24" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="M24" s="21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="110.25" customHeight="1">
+      <c r="D25" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="M25" s="21" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="77.25" customHeight="1">
-      <c r="A20" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="L20" s="19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="87.75" customHeight="1">
-      <c r="B21" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="E21" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="G21" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="H21" s="7"/>
-      <c r="I21" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="L21" s="18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="96.75" customHeight="1">
-      <c r="B22" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="G22" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="I22" s="21" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="117" customHeight="1">
-      <c r="B23" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="I23" s="21" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="75.75" customHeight="1">
-      <c r="B24" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="I24" s="21" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="110.25" customHeight="1">
-      <c r="D25" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="I25" s="21" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -3077,16 +3213,16 @@
         <v>31</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D3" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>124</v>
-      </c>
       <c r="F3" s="11" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="24.95" customHeight="1">
@@ -3094,13 +3230,13 @@
         <v>32</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="F4" s="8"/>
     </row>
@@ -3271,7 +3407,7 @@
     </row>
     <row r="16" spans="2:6" s="23" customFormat="1" ht="24.95" customHeight="1">
       <c r="B16" s="13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C16" s="14">
         <v>12</v>
@@ -3301,7 +3437,7 @@
     </row>
     <row r="18" spans="1:6" ht="78" customHeight="1">
       <c r="B18" s="9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="19"/>
@@ -3310,7 +3446,7 @@
     </row>
     <row r="19" spans="1:6" ht="62.25" customHeight="1">
       <c r="B19" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C19" s="19"/>
       <c r="D19" s="19"/>
@@ -3319,10 +3455,10 @@
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1">
       <c r="A20" s="39" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C20" s="30">
         <v>40</v>
@@ -3338,7 +3474,7 @@
     <row r="21" spans="1:6">
       <c r="A21" s="39"/>
       <c r="B21" s="27" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C21" s="31">
         <v>30</v>
@@ -3353,7 +3489,7 @@
     <row r="22" spans="1:6">
       <c r="A22" s="39"/>
       <c r="B22" s="27" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C22" s="31">
         <v>28</v>
@@ -3368,7 +3504,7 @@
     <row r="23" spans="1:6">
       <c r="A23" s="39"/>
       <c r="B23" s="27" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C23" s="30">
         <v>45</v>
@@ -3383,7 +3519,7 @@
     <row r="24" spans="1:6">
       <c r="A24" s="39"/>
       <c r="B24" s="27" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C24" s="30">
         <v>40</v>
@@ -3398,7 +3534,7 @@
     <row r="25" spans="1:6">
       <c r="A25" s="39"/>
       <c r="B25" s="27" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C25" s="30">
         <v>32</v>
@@ -3413,7 +3549,7 @@
     <row r="26" spans="1:6">
       <c r="A26" s="39"/>
       <c r="B26" s="27" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C26" s="30">
         <v>50</v>
@@ -3428,7 +3564,7 @@
     <row r="27" spans="1:6">
       <c r="A27" s="39"/>
       <c r="B27" s="27" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C27" s="30">
         <v>35</v>
@@ -3443,7 +3579,7 @@
     <row r="28" spans="1:6">
       <c r="A28" s="39"/>
       <c r="B28" s="27" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C28" s="30">
         <v>30</v>
@@ -3458,7 +3594,7 @@
     <row r="29" spans="1:6">
       <c r="A29" s="39"/>
       <c r="B29" s="27" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C29" s="30">
         <v>35</v>
@@ -3473,7 +3609,7 @@
     <row r="30" spans="1:6">
       <c r="A30" s="39"/>
       <c r="B30" s="27" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C30" s="30">
         <v>35</v>
@@ -3488,7 +3624,7 @@
     <row r="31" spans="1:6">
       <c r="A31" s="39"/>
       <c r="B31" s="27" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C31" s="30">
         <v>50</v>
@@ -3503,7 +3639,7 @@
     <row r="32" spans="1:6">
       <c r="A32" s="39"/>
       <c r="B32" s="27" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C32" s="30">
         <v>45</v>
@@ -3518,7 +3654,7 @@
     <row r="33" spans="1:5">
       <c r="A33" s="39"/>
       <c r="B33" s="27" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C33" s="30">
         <v>35</v>
@@ -3533,7 +3669,7 @@
     <row r="34" spans="1:5">
       <c r="A34" s="39"/>
       <c r="B34" s="27" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C34" s="30">
         <v>40</v>
@@ -3548,7 +3684,7 @@
     <row r="35" spans="1:5">
       <c r="A35" s="39"/>
       <c r="B35" s="27" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C35" s="30">
         <v>32</v>
@@ -3563,7 +3699,7 @@
     <row r="36" spans="1:5">
       <c r="A36" s="39"/>
       <c r="B36" s="27" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C36" s="30">
         <v>43</v>
@@ -3578,7 +3714,7 @@
     <row r="37" spans="1:5">
       <c r="A37" s="39"/>
       <c r="B37" s="27" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C37" s="30">
         <v>40</v>
@@ -3593,7 +3729,7 @@
     <row r="38" spans="1:5">
       <c r="A38" s="39"/>
       <c r="B38" s="27" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C38" s="30">
         <v>40</v>
@@ -3608,7 +3744,7 @@
     <row r="39" spans="1:5">
       <c r="A39" s="39"/>
       <c r="B39" s="27" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C39" s="30">
         <v>30</v>
@@ -3627,10 +3763,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="38" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C41" s="30">
         <v>35</v>
@@ -3641,7 +3777,7 @@
     <row r="42" spans="1:5">
       <c r="A42" s="38"/>
       <c r="B42" s="27" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C42" s="30">
         <v>35</v>
@@ -3654,7 +3790,7 @@
     <row r="43" spans="1:5">
       <c r="A43" s="38"/>
       <c r="B43" s="27" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C43" s="30"/>
       <c r="D43" s="31"/>
@@ -3665,7 +3801,7 @@
     <row r="44" spans="1:5">
       <c r="A44" s="38"/>
       <c r="B44" s="27" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C44" s="30"/>
       <c r="D44" s="31"/>
@@ -3676,7 +3812,7 @@
     <row r="45" spans="1:5">
       <c r="A45" s="38"/>
       <c r="B45" s="27" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C45" s="30"/>
       <c r="D45" s="31"/>
@@ -3687,7 +3823,7 @@
     <row r="46" spans="1:5">
       <c r="A46" s="38"/>
       <c r="B46" s="27" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C46" s="30"/>
       <c r="D46" s="31"/>
@@ -3698,7 +3834,7 @@
     <row r="47" spans="1:5">
       <c r="A47" s="38"/>
       <c r="B47" s="27" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C47" s="32">
         <v>38</v>
@@ -3709,7 +3845,7 @@
     <row r="48" spans="1:5">
       <c r="A48" s="38"/>
       <c r="B48" s="27" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C48" s="30">
         <v>36</v>
@@ -3720,7 +3856,7 @@
     <row r="49" spans="1:5">
       <c r="A49" s="38"/>
       <c r="B49" s="27" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C49" s="30">
         <v>40</v>
@@ -3733,7 +3869,7 @@
     <row r="50" spans="1:5">
       <c r="A50" s="38"/>
       <c r="B50" s="27" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C50" s="32">
         <v>35</v>
@@ -3744,7 +3880,7 @@
     <row r="51" spans="1:5">
       <c r="A51" s="38"/>
       <c r="B51" s="27" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C51" s="32">
         <v>35</v>
@@ -3759,77 +3895,77 @@
     </row>
     <row r="53" spans="1:5">
       <c r="B53" s="40" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="B54" s="40"/>
       <c r="C54" s="29" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="B55" s="40"/>
       <c r="C55" s="29" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="B56" s="40"/>
       <c r="C56" s="29" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E56" s="29" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="B57" s="40"/>
       <c r="C57" s="29" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E57" s="29" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="B58" s="40"/>
       <c r="C58" s="29" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D58" s="28"/>
     </row>
     <row r="59" spans="1:5">
       <c r="B59" s="40"/>
       <c r="C59" s="29" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D59" s="28"/>
     </row>
